--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7860" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7860" uniqueCount="836">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1147,6 +1147,15 @@
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R355-TypeIdentifiantOffre/FHIR/TRE-R355-TypeIdentifiantOffre"/&gt;
+    &lt;code value="35"/&gt;
+    &lt;display value="Identifiant fonctionnel de l'offre connu par l'instance ROR"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -10567,7 +10576,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>356</v>
       </c>
@@ -10580,13 +10589,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -10617,7 +10626,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -10635,10 +10644,10 @@
         <v>151</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -10656,7 +10665,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10682,10 +10691,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10711,16 +10720,16 @@
         <v>130</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10733,7 +10742,7 @@
         <v>75</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>75</v>
@@ -10769,7 +10778,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10787,7 +10796,7 @@
         <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>75</v>
@@ -10795,10 +10804,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10824,13 +10833,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10844,7 +10853,7 @@
         <v>75</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>75</v>
@@ -10880,7 +10889,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10898,7 +10907,7 @@
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>75</v>
@@ -10906,10 +10915,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10932,13 +10941,13 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10989,7 +10998,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -11007,7 +11016,7 @@
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>75</v>
@@ -11015,10 +11024,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11041,16 +11050,16 @@
         <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11100,7 +11109,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11118,7 +11127,7 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>75</v>
@@ -11126,10 +11135,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11152,23 +11161,23 @@
         <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="R75" t="s" s="2">
         <v>75</v>
@@ -11213,7 +11222,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11228,21 +11237,21 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11265,16 +11274,16 @@
         <v>86</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11324,7 +11333,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11339,10 +11348,10 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
@@ -11350,14 +11359,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11379,13 +11388,13 @@
         <v>235</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11415,7 +11424,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -11433,7 +11442,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11448,25 +11457,25 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11488,10 +11497,10 @@
         <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11522,7 +11531,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -11540,7 +11549,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11555,10 +11564,10 @@
         <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>75</v>
@@ -11566,10 +11575,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11595,10 +11604,10 @@
         <v>235</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11629,13 +11638,13 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AC79" s="2"/>
       <c r="AD79" t="s" s="2">
@@ -11645,7 +11654,7 @@
         <v>114</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11663,7 +11672,7 @@
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>75</v>
@@ -11671,13 +11680,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>75</v>
@@ -11702,10 +11711,10 @@
         <v>235</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11736,7 +11745,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11754,7 +11763,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11769,10 +11778,10 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>75</v>
@@ -11780,13 +11789,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>75</v>
@@ -11811,10 +11820,10 @@
         <v>235</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11845,7 +11854,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>75</v>
@@ -11863,7 +11872,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11878,10 +11887,10 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>75</v>
@@ -11889,10 +11898,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11915,13 +11924,13 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11972,7 +11981,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11987,21 +11996,21 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12027,10 +12036,10 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12081,7 +12090,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12096,10 +12105,10 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>75</v>
@@ -12107,10 +12116,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12136,13 +12145,13 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12192,7 +12201,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12207,10 +12216,10 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>75</v>
@@ -12218,10 +12227,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12244,13 +12253,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12301,7 +12310,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12319,7 +12328,7 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
@@ -12327,10 +12336,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12353,13 +12362,13 @@
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12410,7 +12419,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12428,7 +12437,7 @@
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
@@ -12436,10 +12445,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12462,16 +12471,16 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12521,7 +12530,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12536,10 +12545,10 @@
         <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
@@ -12547,10 +12556,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12656,10 +12665,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12765,13 +12774,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="B90" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="C90" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>75</v>
@@ -12793,13 +12802,13 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12876,13 +12885,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>75</v>
@@ -12904,13 +12913,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12987,13 +12996,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -13015,13 +13024,13 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13098,13 +13107,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>75</v>
@@ -13126,13 +13135,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13209,10 +13218,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13238,10 +13247,10 @@
         <v>175</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13271,10 +13280,10 @@
         <v>166</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>75</v>
@@ -13292,7 +13301,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13301,7 +13310,7 @@
         <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>98</v>
@@ -13310,7 +13319,7 @@
         <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>75</v>
@@ -13318,10 +13327,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13347,16 +13356,16 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -13405,7 +13414,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13423,7 +13432,7 @@
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>75</v>
@@ -13431,10 +13440,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13460,16 +13469,16 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -13497,10 +13506,10 @@
         <v>166</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13518,7 +13527,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13536,7 +13545,7 @@
         <v>75</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>75</v>
@@ -13544,10 +13553,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13570,16 +13579,16 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13629,7 +13638,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13655,10 +13664,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13681,13 +13690,13 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13738,7 +13747,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13756,7 +13765,7 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>75</v>
@@ -13764,10 +13773,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13790,16 +13799,16 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13849,7 +13858,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13867,7 +13876,7 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>75</v>
@@ -13875,10 +13884,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13904,13 +13913,13 @@
         <v>235</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13939,10 +13948,10 @@
         <v>159</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -13960,7 +13969,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13978,7 +13987,7 @@
         <v>75</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>75</v>
@@ -13986,10 +13995,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14012,13 +14021,13 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14069,7 +14078,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -14095,10 +14104,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14204,10 +14213,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14315,14 +14324,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14344,10 +14353,10 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>111</v>
@@ -14402,7 +14411,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14428,10 +14437,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14457,10 +14466,10 @@
         <v>235</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14490,7 +14499,7 @@
         <v>159</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z105" t="s" s="2">
         <v>75</v>
@@ -14511,7 +14520,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14529,7 +14538,7 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>75</v>
@@ -14537,10 +14546,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14563,16 +14572,16 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14622,7 +14631,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14640,7 +14649,7 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14648,10 +14657,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14677,13 +14686,13 @@
         <v>235</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14712,10 +14721,10 @@
         <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -14733,7 +14742,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14751,7 +14760,7 @@
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
@@ -14759,10 +14768,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14788,13 +14797,13 @@
         <v>235</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14823,7 +14832,7 @@
         <v>159</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z108" t="s" s="2">
         <v>75</v>
@@ -14832,7 +14841,7 @@
         <v>75</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
@@ -14842,7 +14851,7 @@
         <v>114</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14860,7 +14869,7 @@
         <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>75</v>
@@ -14868,10 +14877,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14977,10 +14986,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15088,13 +15097,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>75</v>
@@ -15116,13 +15125,13 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15199,10 +15208,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15228,16 +15237,16 @@
         <v>147</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -15286,7 +15295,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15304,7 +15313,7 @@
         <v>75</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>75</v>
@@ -15312,10 +15321,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15341,16 +15350,16 @@
         <v>101</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -15399,7 +15408,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15417,7 +15426,7 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>75</v>
@@ -15425,13 +15434,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>75</v>
@@ -15456,13 +15465,13 @@
         <v>235</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15492,7 +15501,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>75</v>
@@ -15510,7 +15519,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15525,10 +15534,10 @@
         <v>98</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>75</v>
@@ -15536,10 +15545,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15645,10 +15654,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15756,13 +15765,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>75</v>
@@ -15784,13 +15793,13 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15867,10 +15876,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15896,16 +15905,16 @@
         <v>147</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15954,7 +15963,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15972,7 +15981,7 @@
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>75</v>
@@ -15980,10 +15989,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16009,16 +16018,16 @@
         <v>101</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -16067,7 +16076,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -16085,7 +16094,7 @@
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>75</v>
@@ -16093,13 +16102,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>75</v>
@@ -16124,13 +16133,13 @@
         <v>235</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16160,7 +16169,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
@@ -16178,7 +16187,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16193,10 +16202,10 @@
         <v>98</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>75</v>
@@ -16204,10 +16213,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16313,10 +16322,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16424,13 +16433,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>75</v>
@@ -16452,13 +16461,13 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16535,10 +16544,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16564,16 +16573,16 @@
         <v>147</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -16622,7 +16631,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16640,7 +16649,7 @@
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>75</v>
@@ -16648,10 +16657,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16677,16 +16686,16 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
@@ -16735,7 +16744,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16753,7 +16762,7 @@
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>75</v>
@@ -16761,13 +16770,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>75</v>
@@ -16792,13 +16801,13 @@
         <v>235</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16828,7 +16837,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -16846,7 +16855,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16861,10 +16870,10 @@
         <v>98</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>75</v>
@@ -16872,10 +16881,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16981,10 +16990,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17092,13 +17101,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>75</v>
@@ -17120,13 +17129,13 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17203,10 +17212,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17232,16 +17241,16 @@
         <v>147</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -17290,7 +17299,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17308,7 +17317,7 @@
         <v>75</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>75</v>
@@ -17316,10 +17325,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17345,16 +17354,16 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>75</v>
@@ -17403,7 +17412,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17421,7 +17430,7 @@
         <v>75</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>75</v>
@@ -17429,13 +17438,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>75</v>
@@ -17460,13 +17469,13 @@
         <v>235</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17496,7 +17505,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>75</v>
@@ -17514,7 +17523,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17529,10 +17538,10 @@
         <v>98</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>75</v>
@@ -17540,10 +17549,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17649,10 +17658,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17760,13 +17769,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>75</v>
@@ -17788,13 +17797,13 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17871,10 +17880,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17900,16 +17909,16 @@
         <v>147</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>75</v>
@@ -17958,7 +17967,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17976,7 +17985,7 @@
         <v>75</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>75</v>
@@ -17984,10 +17993,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18013,16 +18022,16 @@
         <v>101</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>75</v>
@@ -18071,7 +18080,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18089,7 +18098,7 @@
         <v>75</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>75</v>
@@ -18097,13 +18106,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>75</v>
@@ -18128,13 +18137,13 @@
         <v>235</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18164,7 +18173,7 @@
       </c>
       <c r="Y138" s="2"/>
       <c r="Z138" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
@@ -18182,7 +18191,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18197,10 +18206,10 @@
         <v>98</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>75</v>
@@ -18208,10 +18217,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18317,10 +18326,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18426,13 +18435,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>75</v>
@@ -18454,13 +18463,13 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18537,10 +18546,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18646,10 +18655,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18755,10 +18764,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18798,7 +18807,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>75</v>
@@ -18866,10 +18875,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18910,7 +18919,7 @@
         <v>75</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>75</v>
@@ -18929,7 +18938,7 @@
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>75</v>
@@ -18973,10 +18982,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19002,16 +19011,16 @@
         <v>147</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>75</v>
@@ -19060,7 +19069,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -19078,7 +19087,7 @@
         <v>75</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>75</v>
@@ -19086,10 +19095,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19115,16 +19124,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>75</v>
@@ -19173,7 +19182,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19191,7 +19200,7 @@
         <v>75</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>75</v>
@@ -19199,13 +19208,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>75</v>
@@ -19230,13 +19239,13 @@
         <v>235</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19266,7 +19275,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>75</v>
@@ -19284,7 +19293,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19299,10 +19308,10 @@
         <v>98</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>75</v>
@@ -19310,10 +19319,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19419,10 +19428,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19528,13 +19537,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>75</v>
@@ -19556,13 +19565,13 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19639,10 +19648,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19748,10 +19757,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19857,10 +19866,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19900,7 +19909,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>75</v>
@@ -19968,10 +19977,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20012,7 +20021,7 @@
         <v>75</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>75</v>
@@ -20031,7 +20040,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>75</v>
@@ -20075,10 +20084,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20104,16 +20113,16 @@
         <v>147</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>75</v>
@@ -20162,7 +20171,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20180,7 +20189,7 @@
         <v>75</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>75</v>
@@ -20188,10 +20197,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20217,16 +20226,16 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>75</v>
@@ -20275,7 +20284,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20293,7 +20302,7 @@
         <v>75</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>75</v>
@@ -20301,13 +20310,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>75</v>
@@ -20332,13 +20341,13 @@
         <v>235</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -20368,7 +20377,7 @@
       </c>
       <c r="Y158" s="2"/>
       <c r="Z158" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>75</v>
@@ -20386,7 +20395,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -20401,10 +20410,10 @@
         <v>98</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>75</v>
@@ -20412,10 +20421,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20521,10 +20530,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20632,13 +20641,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>75</v>
@@ -20660,13 +20669,13 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20743,10 +20752,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20772,16 +20781,16 @@
         <v>147</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>75</v>
@@ -20830,7 +20839,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20848,7 +20857,7 @@
         <v>75</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>75</v>
@@ -20856,10 +20865,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20885,16 +20894,16 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>75</v>
@@ -20943,7 +20952,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20961,7 +20970,7 @@
         <v>75</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>75</v>
@@ -20969,13 +20978,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>75</v>
@@ -21000,13 +21009,13 @@
         <v>235</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -21036,7 +21045,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -21054,7 +21063,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -21069,10 +21078,10 @@
         <v>98</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>75</v>
@@ -21080,10 +21089,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21189,10 +21198,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21300,13 +21309,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>75</v>
@@ -21328,13 +21337,13 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -21411,10 +21420,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21440,16 +21449,16 @@
         <v>147</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>75</v>
@@ -21498,7 +21507,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21516,7 +21525,7 @@
         <v>75</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>75</v>
@@ -21524,10 +21533,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21553,16 +21562,16 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>75</v>
@@ -21611,7 +21620,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21629,7 +21638,7 @@
         <v>75</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>75</v>
@@ -21637,13 +21646,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>75</v>
@@ -21668,13 +21677,13 @@
         <v>235</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21704,7 +21713,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -21722,7 +21731,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21737,10 +21746,10 @@
         <v>98</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>75</v>
@@ -21748,10 +21757,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21857,10 +21866,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21968,13 +21977,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>75</v>
@@ -21996,13 +22005,13 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -22079,10 +22088,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22108,16 +22117,16 @@
         <v>147</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>75</v>
@@ -22166,7 +22175,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22184,7 +22193,7 @@
         <v>75</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>75</v>
@@ -22192,10 +22201,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22221,16 +22230,16 @@
         <v>101</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>75</v>
@@ -22279,7 +22288,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22297,7 +22306,7 @@
         <v>75</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>75</v>
@@ -22305,13 +22314,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>75</v>
@@ -22336,13 +22345,13 @@
         <v>235</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -22372,7 +22381,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>75</v>
@@ -22390,7 +22399,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22405,10 +22414,10 @@
         <v>98</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>75</v>
@@ -22416,10 +22425,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22525,10 +22534,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22636,13 +22645,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>75</v>
@@ -22664,13 +22673,13 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -22747,10 +22756,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22776,16 +22785,16 @@
         <v>147</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>75</v>
@@ -22834,7 +22843,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22852,7 +22861,7 @@
         <v>75</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>75</v>
@@ -22860,10 +22869,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22889,16 +22898,16 @@
         <v>101</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>75</v>
@@ -22947,7 +22956,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22965,7 +22974,7 @@
         <v>75</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>75</v>
@@ -22973,13 +22982,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>75</v>
@@ -23004,13 +23013,13 @@
         <v>235</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23040,7 +23049,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>75</v>
@@ -23058,7 +23067,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -23073,10 +23082,10 @@
         <v>98</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>75</v>
@@ -23084,10 +23093,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23193,10 +23202,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23304,13 +23313,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>75</v>
@@ -23332,13 +23341,13 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -23415,10 +23424,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23444,16 +23453,16 @@
         <v>147</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>75</v>
@@ -23502,7 +23511,7 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23520,7 +23529,7 @@
         <v>75</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>75</v>
@@ -23528,10 +23537,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23557,16 +23566,16 @@
         <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>75</v>
@@ -23615,7 +23624,7 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23633,7 +23642,7 @@
         <v>75</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>75</v>
@@ -23641,13 +23650,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D188" t="s" s="2">
         <v>75</v>
@@ -23672,13 +23681,13 @@
         <v>235</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -23708,7 +23717,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>75</v>
@@ -23726,7 +23735,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23741,10 +23750,10 @@
         <v>98</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>75</v>
@@ -23752,10 +23761,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23861,10 +23870,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23972,13 +23981,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>75</v>
@@ -24000,13 +24009,13 @@
         <v>75</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -24083,10 +24092,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24112,16 +24121,16 @@
         <v>147</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>75</v>
@@ -24170,7 +24179,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -24188,7 +24197,7 @@
         <v>75</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>75</v>
@@ -24196,10 +24205,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24225,16 +24234,16 @@
         <v>101</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>75</v>
@@ -24283,7 +24292,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -24301,7 +24310,7 @@
         <v>75</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>75</v>
@@ -24309,10 +24318,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24338,13 +24347,13 @@
         <v>235</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -24394,7 +24403,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24420,10 +24429,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24449,10 +24458,10 @@
         <v>235</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -24482,10 +24491,10 @@
         <v>159</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>75</v>
@@ -24503,7 +24512,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24521,7 +24530,7 @@
         <v>75</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>75</v>
@@ -24529,10 +24538,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24555,13 +24564,13 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24612,7 +24621,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24630,7 +24639,7 @@
         <v>75</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>75</v>
@@ -24638,10 +24647,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24664,16 +24673,16 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -24723,7 +24732,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>76</v>
@@ -24738,10 +24747,10 @@
         <v>98</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>75</v>
@@ -24749,10 +24758,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24858,10 +24867,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24965,13 +24974,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="B200" t="s" s="2">
-        <v>748</v>
-      </c>
       <c r="C200" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>75</v>
@@ -24993,13 +25002,13 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -25076,13 +25085,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>75</v>
@@ -25104,13 +25113,13 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -25187,13 +25196,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>75</v>
@@ -25215,13 +25224,13 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -25298,14 +25307,14 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
@@ -25327,10 +25336,10 @@
         <v>108</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N203" t="s" s="2">
         <v>111</v>
@@ -25385,7 +25394,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25411,10 +25420,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25440,10 +25449,10 @@
         <v>175</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -25473,10 +25482,10 @@
         <v>166</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>75</v>
@@ -25494,7 +25503,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>76</v>
@@ -25512,7 +25521,7 @@
         <v>75</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>75</v>
@@ -25520,10 +25529,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25546,13 +25555,13 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -25603,7 +25612,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>76</v>
@@ -25621,7 +25630,7 @@
         <v>75</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>75</v>
@@ -25629,10 +25638,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25655,16 +25664,16 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -25714,7 +25723,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>76</v>
@@ -25729,10 +25738,10 @@
         <v>98</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>75</v>
@@ -25740,10 +25749,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25766,16 +25775,16 @@
         <v>75</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -25825,7 +25834,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>76</v>
@@ -25840,10 +25849,10 @@
         <v>98</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>75</v>
@@ -25851,10 +25860,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25877,13 +25886,13 @@
         <v>75</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -25922,7 +25931,7 @@
         <v>75</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AC208" s="2"/>
       <c r="AD208" t="s" s="2">
@@ -25932,7 +25941,7 @@
         <v>114</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25950,7 +25959,7 @@
         <v>75</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>75</v>
@@ -25958,10 +25967,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26067,10 +26076,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26178,14 +26187,14 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -26207,10 +26216,10 @@
         <v>108</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N211" t="s" s="2">
         <v>111</v>
@@ -26265,7 +26274,7 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>76</v>
@@ -26291,10 +26300,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26320,10 +26329,10 @@
         <v>101</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -26374,7 +26383,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>85</v>
@@ -26400,10 +26409,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26426,13 +26435,13 @@
         <v>75</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -26483,7 +26492,7 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -26501,7 +26510,7 @@
         <v>75</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>75</v>
@@ -26509,13 +26518,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D214" t="s" s="2">
         <v>75</v>
@@ -26537,13 +26546,13 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -26594,7 +26603,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>76</v>
@@ -26612,7 +26621,7 @@
         <v>75</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>75</v>
@@ -26620,10 +26629,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26664,7 +26673,7 @@
         <v>75</v>
       </c>
       <c r="S215" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="T215" t="s" s="2">
         <v>75</v>
@@ -26729,10 +26738,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26840,14 +26849,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -26869,10 +26878,10 @@
         <v>108</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N217" t="s" s="2">
         <v>111</v>
@@ -26927,7 +26936,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26953,10 +26962,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26982,10 +26991,10 @@
         <v>101</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -26997,7 +27006,7 @@
         <v>75</v>
       </c>
       <c r="S218" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="T218" t="s" s="2">
         <v>75</v>
@@ -27036,7 +27045,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>85</v>
@@ -27062,10 +27071,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27088,13 +27097,13 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -27145,7 +27154,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -27163,7 +27172,7 @@
         <v>75</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>75</v>
@@ -27171,10 +27180,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -27280,10 +27289,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -27391,10 +27400,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27417,16 +27426,16 @@
         <v>86</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
@@ -27476,7 +27485,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27485,16 +27494,16 @@
         <v>85</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AM222" t="s" s="2">
         <v>75</v>
@@ -27502,10 +27511,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27528,23 +27537,23 @@
         <v>86</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q223" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="R223" t="s" s="2">
         <v>75</v>
@@ -27589,7 +27598,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>76</v>
@@ -27598,16 +27607,16 @@
         <v>85</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AM223" t="s" s="2">
         <v>75</v>
@@ -27615,10 +27624,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27644,10 +27653,10 @@
         <v>101</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -27698,7 +27707,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>76</v>
@@ -27716,7 +27725,7 @@
         <v>75</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>75</v>
@@ -27724,10 +27733,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27750,13 +27759,13 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -27807,7 +27816,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>76</v>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
